--- a/交易机会统计(已自动还原).xlsx
+++ b/交易机会统计(已自动还原).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\EURUSD案例库\case-overview-images\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29EA50F8-192E-4231-BEDD-DEA4DD49E8AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1679EEE8-B956-487A-BBC8-298CDFD43EBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="889" uniqueCount="124">
   <si>
     <t>年限</t>
   </si>
@@ -289,6 +289,114 @@
   </si>
   <si>
     <t>EUR28</t>
+  </si>
+  <si>
+    <t>EUR29</t>
+  </si>
+  <si>
+    <t>EUR30</t>
+  </si>
+  <si>
+    <t>大通道下边线</t>
+  </si>
+  <si>
+    <t>EUR31</t>
+  </si>
+  <si>
+    <t>积累区间内部</t>
+  </si>
+  <si>
+    <t>EUR32</t>
+  </si>
+  <si>
+    <t>处于大积累区间上边线</t>
+  </si>
+  <si>
+    <t>EUR33</t>
+  </si>
+  <si>
+    <t>无释放</t>
+  </si>
+  <si>
+    <t>EUR34</t>
+  </si>
+  <si>
+    <t>EUR35</t>
+  </si>
+  <si>
+    <t>EUR36</t>
+  </si>
+  <si>
+    <t>EUR37</t>
+  </si>
+  <si>
+    <t>EUR38</t>
+  </si>
+  <si>
+    <t>复合头肩顶</t>
+  </si>
+  <si>
+    <t>EUR39</t>
+  </si>
+  <si>
+    <t>EUR40</t>
+  </si>
+  <si>
+    <t>EUR41</t>
+  </si>
+  <si>
+    <t>EUR42</t>
+  </si>
+  <si>
+    <t>EUR43</t>
+  </si>
+  <si>
+    <t>EUR44</t>
+  </si>
+  <si>
+    <t>上旗子</t>
+  </si>
+  <si>
+    <t>EUR45</t>
+  </si>
+  <si>
+    <t>EUR46</t>
+  </si>
+  <si>
+    <t>EUR47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">双头 </t>
+  </si>
+  <si>
+    <t>EUR48</t>
+  </si>
+  <si>
+    <t>EUR49</t>
+  </si>
+  <si>
+    <t>EUR50</t>
+  </si>
+  <si>
+    <t>EUR51</t>
+  </si>
+  <si>
+    <t>EUR52</t>
+  </si>
+  <si>
+    <t>EUR53</t>
+  </si>
+  <si>
+    <t>EUR54</t>
+  </si>
+  <si>
+    <t>EUR55</t>
+  </si>
+  <si>
+    <t>EUR56</t>
+  </si>
+  <si>
+    <t>EUR57</t>
   </si>
 </sst>
 </file>
@@ -626,7 +734,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R35"/>
+  <dimension ref="A1:R58"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.85546875" customWidth="1"/>
@@ -2274,120 +2382,1628 @@
       </c>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A30" s="1"/>
-      <c r="B30" s="1"/>
-      <c r="C30" s="1"/>
-      <c r="D30" s="1"/>
-      <c r="E30" s="1"/>
-      <c r="F30" s="1"/>
-      <c r="G30" s="1"/>
-      <c r="H30" s="1"/>
-      <c r="I30" s="1"/>
-      <c r="J30" s="1"/>
-      <c r="K30" s="1"/>
-      <c r="L30" s="1"/>
-      <c r="M30" s="1"/>
-      <c r="N30" s="1"/>
-      <c r="O30" s="1"/>
-      <c r="P30" s="1"/>
-      <c r="Q30" s="1"/>
+      <c r="A30" s="1">
+        <v>2006</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K30" s="1">
+        <v>9</v>
+      </c>
+      <c r="L30" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="M30" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="N30" s="1">
+        <v>5</v>
+      </c>
+      <c r="O30" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P30" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q30" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="R30" s="1" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A31" s="1"/>
-      <c r="B31" s="1"/>
-      <c r="C31" s="1"/>
-      <c r="D31" s="1"/>
-      <c r="E31" s="1"/>
-      <c r="F31" s="1"/>
-      <c r="G31" s="1"/>
-      <c r="H31" s="1"/>
-      <c r="I31" s="1"/>
-      <c r="J31" s="1"/>
-      <c r="K31" s="1"/>
-      <c r="L31" s="1"/>
-      <c r="M31" s="1"/>
-      <c r="N31" s="1"/>
-      <c r="O31" s="1"/>
-      <c r="P31" s="1"/>
-      <c r="Q31" s="1"/>
+      <c r="A31" s="1">
+        <v>2006</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K31" s="1">
+        <v>6</v>
+      </c>
+      <c r="L31" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="M31" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="N31" s="1">
+        <v>4</v>
+      </c>
+      <c r="O31" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P31" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q31" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="R31" s="1" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A32" s="1"/>
-      <c r="B32" s="1"/>
-      <c r="C32" s="1"/>
-      <c r="D32" s="1"/>
-      <c r="E32" s="1"/>
-      <c r="F32" s="1"/>
-      <c r="G32" s="1"/>
-      <c r="H32" s="1"/>
-      <c r="I32" s="1"/>
-      <c r="J32" s="1"/>
-      <c r="K32" s="1"/>
-      <c r="L32" s="1"/>
-      <c r="M32" s="1"/>
-      <c r="N32" s="1"/>
-      <c r="O32" s="1"/>
-      <c r="P32" s="1"/>
-      <c r="Q32" s="1"/>
-      <c r="R32" s="1"/>
+      <c r="A32" s="1">
+        <v>2006</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K32" s="1">
+        <v>20</v>
+      </c>
+      <c r="L32" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="M32" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="N32" s="1">
+        <v>4</v>
+      </c>
+      <c r="O32" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P32" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q32" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="R32" s="1" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A33" s="1"/>
-      <c r="B33" s="1"/>
-      <c r="C33" s="1"/>
-      <c r="D33" s="1"/>
-      <c r="E33" s="1"/>
-      <c r="F33" s="1"/>
-      <c r="G33" s="1"/>
-      <c r="H33" s="1"/>
-      <c r="I33" s="1"/>
-      <c r="J33" s="1"/>
-      <c r="K33" s="1"/>
-      <c r="L33" s="1"/>
-      <c r="M33" s="1"/>
-      <c r="N33" s="1"/>
-      <c r="O33" s="1"/>
-      <c r="P33" s="1"/>
-      <c r="Q33" s="1"/>
-      <c r="R33" s="1"/>
+      <c r="A33" s="1">
+        <v>2006</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K33" s="1">
+        <v>5</v>
+      </c>
+      <c r="L33" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M33" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="N33" s="1">
+        <v>3</v>
+      </c>
+      <c r="O33" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P33" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q33" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="R33" s="1" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A34" s="1"/>
-      <c r="B34" s="1"/>
-      <c r="C34" s="1"/>
-      <c r="D34" s="1"/>
-      <c r="E34" s="1"/>
-      <c r="F34" s="1"/>
-      <c r="G34" s="1"/>
-      <c r="H34" s="1"/>
-      <c r="I34" s="1"/>
-      <c r="J34" s="1"/>
-      <c r="K34" s="1"/>
-      <c r="L34" s="1"/>
-      <c r="M34" s="1"/>
-      <c r="N34" s="1"/>
-      <c r="O34" s="1"/>
-      <c r="P34" s="1"/>
-      <c r="Q34" s="1"/>
+      <c r="A34" s="1">
+        <v>2006</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="K34" s="1">
+        <v>10</v>
+      </c>
+      <c r="L34" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M34" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="N34" s="1">
+        <v>6</v>
+      </c>
+      <c r="O34" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P34" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q34" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="R34" s="1" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A35" s="1"/>
-      <c r="B35" s="1"/>
-      <c r="C35" s="1"/>
-      <c r="D35" s="1"/>
-      <c r="E35" s="1"/>
-      <c r="F35" s="1"/>
-      <c r="G35" s="1"/>
-      <c r="H35" s="1"/>
-      <c r="I35" s="1"/>
-      <c r="J35" s="1"/>
-      <c r="K35" s="1"/>
-      <c r="L35" s="1"/>
-      <c r="M35" s="1"/>
-      <c r="N35" s="1"/>
-      <c r="O35" s="1"/>
-      <c r="P35" s="1"/>
-      <c r="Q35" s="1"/>
+      <c r="A35" s="1">
+        <v>2007</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L35" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="M35" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N35" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="O35" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P35" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q35" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="R35" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A36" s="1">
+        <v>2007</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="K36" s="1">
+        <v>2</v>
+      </c>
+      <c r="L36" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="M36" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N36" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="O36" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P36" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q36" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="R36" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A37" s="1">
+        <v>2007</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K37" s="1">
+        <v>6</v>
+      </c>
+      <c r="L37" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="M37" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="N37" s="1">
+        <v>2</v>
+      </c>
+      <c r="O37" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P37" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q37" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="R37" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A38" s="1">
+        <v>2007</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K38" s="1">
+        <v>8</v>
+      </c>
+      <c r="L38" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M38" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="N38" s="1">
+        <v>6</v>
+      </c>
+      <c r="O38" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P38" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q38" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="R38" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A39" s="1">
+        <v>2007</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I39" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J39" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K39" s="1">
+        <v>8</v>
+      </c>
+      <c r="L39" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M39" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="N39" s="1">
+        <v>6</v>
+      </c>
+      <c r="O39" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P39" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q39" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="R39" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A40" s="1">
+        <v>2008</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J40" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K40" s="1">
+        <v>6</v>
+      </c>
+      <c r="L40" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="M40" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="N40" s="1">
+        <v>2</v>
+      </c>
+      <c r="O40" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P40" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q40" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="R40" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="1">
+        <v>2008</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J41" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K41" s="1">
+        <v>6</v>
+      </c>
+      <c r="L41" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="M41" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="N41" s="1">
+        <v>2</v>
+      </c>
+      <c r="O41" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P41" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q41" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="R41" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A42" s="1">
+        <v>2008</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J42" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="K42" s="1">
+        <v>10</v>
+      </c>
+      <c r="L42" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="M42" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N42" s="1">
+        <v>8</v>
+      </c>
+      <c r="O42" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P42" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q42" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="R42" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A43" s="1">
+        <v>2008</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J43" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K43" s="1">
+        <v>6</v>
+      </c>
+      <c r="L43" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M43" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="N43" s="1">
+        <v>2</v>
+      </c>
+      <c r="O43" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P43" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q43" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="R43" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A44" s="1">
+        <v>2008</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I44" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J44" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="K44" s="1">
+        <v>4</v>
+      </c>
+      <c r="L44" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="M44" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N44" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="O44" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P44" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q44" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="R44" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A45" s="1">
+        <v>2008</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I45" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J45" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K45" s="1">
+        <v>6</v>
+      </c>
+      <c r="L45" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="M45" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N45" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="O45" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P45" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q45" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="R45" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A46" s="1">
+        <v>2008</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J46" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K46" s="1">
+        <v>10</v>
+      </c>
+      <c r="L46" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="M46" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="N46" s="1">
+        <v>6</v>
+      </c>
+      <c r="O46" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P46" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q46" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="R46" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A47" s="1">
+        <v>2008</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I47" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J47" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K47" s="1">
+        <v>10</v>
+      </c>
+      <c r="L47" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="M47" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="N47" s="1">
+        <v>6</v>
+      </c>
+      <c r="O47" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P47" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q47" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="R47" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A48" s="1">
+        <v>2009</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I48" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J48" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K48" s="1">
+        <v>2</v>
+      </c>
+      <c r="L48" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="M48" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N48" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="O48" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P48" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q48" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="R48" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A49" s="1">
+        <v>2009</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I49" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J49" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K49" s="1">
+        <v>4</v>
+      </c>
+      <c r="L49" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="M49" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="N49" s="1">
+        <v>2</v>
+      </c>
+      <c r="O49" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P49" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q49" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="R49" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A50" s="1">
+        <v>2009</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I50" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J50" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="K50" s="1">
+        <v>6</v>
+      </c>
+      <c r="L50" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M50" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="N50" s="1">
+        <v>6</v>
+      </c>
+      <c r="O50" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P50" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q50" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="R50" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A51" s="1">
+        <v>2009</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I51" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J51" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="K51" s="1">
+        <v>3</v>
+      </c>
+      <c r="L51" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="M51" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N51" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="O51" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P51" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q51" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="R51" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A52" s="1">
+        <v>2009</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H52" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I52" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J52" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K52" s="1">
+        <v>10</v>
+      </c>
+      <c r="L52" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M52" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="N52" s="1">
+        <v>5</v>
+      </c>
+      <c r="O52" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P52" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q52" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="R52" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A53" s="1">
+        <v>2009</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I53" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J53" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K53" s="1">
+        <v>5</v>
+      </c>
+      <c r="L53" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="M53" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N53" s="1">
+        <v>2</v>
+      </c>
+      <c r="O53" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P53" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q53" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="R53" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="54" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A54" s="1">
+        <v>2009</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I54" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J54" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K54" s="1">
+        <v>4</v>
+      </c>
+      <c r="L54" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="M54" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="N54" s="1">
+        <v>3</v>
+      </c>
+      <c r="O54" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P54" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q54" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="R54" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="55" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A55" s="1">
+        <v>2009</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H55" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I55" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J55" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K55" s="1">
+        <v>3</v>
+      </c>
+      <c r="L55" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M55" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="N55" s="1">
+        <v>3</v>
+      </c>
+      <c r="O55" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P55" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q55" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="R55" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="56" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A56" s="1">
+        <v>2009</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H56" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I56" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J56" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K56" s="1">
+        <v>3</v>
+      </c>
+      <c r="L56" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="M56" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="N56" s="1">
+        <v>3</v>
+      </c>
+      <c r="O56" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P56" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q56" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="R56" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="57" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A57" s="1">
+        <v>2009</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H57" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I57" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J57" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="K57" s="1">
+        <v>3</v>
+      </c>
+      <c r="L57" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="M57" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="N57" s="1">
+        <v>2</v>
+      </c>
+      <c r="O57" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P57" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q57" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="R57" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A58" s="1">
+        <v>2009</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H58" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I58" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J58" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K58" s="1">
+        <v>7</v>
+      </c>
+      <c r="L58" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="M58" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="N58" s="1">
+        <v>2</v>
+      </c>
+      <c r="O58" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P58" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q58" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="R58" s="1" t="s">
+        <v>123</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/交易机会统计(已自动还原).xlsx
+++ b/交易机会统计(已自动还原).xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1679EEE8-B956-487A-BBC8-298CDFD43EBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
